--- a/data_lake/datos_diarios_preliminares/dt=2026-07-30/Temp-max-julio-26.xlsx
+++ b/data_lake/datos_diarios_preliminares/dt=2026-07-30/Temp-max-julio-26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\02. Datos Diarios\Tablas\Datos hidrometeorologicos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDD3FF44-849A-4A2C-919C-21A7A0FB872A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE9E923-7937-4F1F-9ED1-193A8CBB80A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TMAX_PRINCIPALES_CIUDADES" sheetId="1" r:id="rId1"/>
@@ -1219,7 +1219,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1412,6 +1412,9 @@
     <xf numFmtId="165" fontId="5" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1435,12 +1438,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -9165,31 +9162,31 @@
         <v>272</v>
       </c>
       <c r="D1" s="32"/>
-      <c r="E1" s="68" t="s">
+      <c r="E1" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
-      <c r="N1" s="68"/>
-      <c r="O1" s="68"/>
-      <c r="P1" s="68"/>
-      <c r="Q1" s="68"/>
-      <c r="R1" s="68"/>
-      <c r="S1" s="68"/>
-      <c r="T1" s="68"/>
-      <c r="U1" s="68"/>
-      <c r="V1" s="68"/>
-      <c r="W1" s="68"/>
-      <c r="X1" s="68"/>
-      <c r="Y1" s="68"/>
-      <c r="Z1" s="68"/>
-      <c r="AA1" s="68"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
+      <c r="P1" s="69"/>
+      <c r="Q1" s="69"/>
+      <c r="R1" s="69"/>
+      <c r="S1" s="69"/>
+      <c r="T1" s="69"/>
+      <c r="U1" s="69"/>
+      <c r="V1" s="69"/>
+      <c r="W1" s="69"/>
+      <c r="X1" s="69"/>
+      <c r="Y1" s="69"/>
+      <c r="Z1" s="69"/>
+      <c r="AA1" s="69"/>
       <c r="AB1" s="35"/>
       <c r="AC1" s="35"/>
       <c r="AD1" s="35"/>
@@ -9514,12 +9511,14 @@
       <c r="AF5" s="57">
         <v>30.1</v>
       </c>
-      <c r="AG5" s="57"/>
+      <c r="AG5" s="57">
+        <v>31.3</v>
+      </c>
       <c r="AH5" s="57"/>
       <c r="AI5" s="57"/>
       <c r="AJ5" s="37">
         <f>+IF(SUM($E5:$AI5)&gt;0,LOOKUP(1000,$E5:$AI5),NA())</f>
-        <v>30.1</v>
+        <v>31.3</v>
       </c>
       <c r="AK5" s="21">
         <f>+MAX($E5:$AI5)</f>
@@ -9537,11 +9536,11 @@
       </c>
       <c r="AO5" s="23">
         <f>IF(COUNTIF(E5:AI5,"&gt;0")&gt;=15,AVERAGE(E5:AI5),"")</f>
-        <v>31.039285714285718</v>
+        <v>31.048275862068969</v>
       </c>
       <c r="AP5" s="23">
         <f>IF(AN5&gt;0,IFERROR(AO5-AN5,""),"")</f>
-        <v>0.84191393827748939</v>
+        <v>0.85090408606074064</v>
       </c>
     </row>
     <row r="6" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9641,12 +9640,14 @@
       <c r="AF6" s="57">
         <v>29.5</v>
       </c>
-      <c r="AG6" s="57"/>
+      <c r="AG6" s="57">
+        <v>30.6</v>
+      </c>
       <c r="AH6" s="57"/>
       <c r="AI6" s="57"/>
       <c r="AJ6" s="37">
         <f t="shared" ref="AJ6:AJ48" si="0">+IF(SUM($E6:$AI6)&gt;0,LOOKUP(1000,$E6:$AI6),NA())</f>
-        <v>29.5</v>
+        <v>30.6</v>
       </c>
       <c r="AK6" s="21">
         <f t="shared" ref="AK6:AK48" si="1">+MAX($E6:$AI6)</f>
@@ -9664,11 +9665,11 @@
       </c>
       <c r="AO6" s="23">
         <f t="shared" ref="AO6:AO15" si="3">IF(COUNTIF(E6:AI6,"&gt;0")&gt;=15,AVERAGE(E6:AI6),"")</f>
-        <v>30.596428571428568</v>
+        <v>30.596551724137928</v>
       </c>
       <c r="AP6" s="23">
         <f t="shared" ref="AP6:AP48" si="4">IF(AN6&gt;0,IFERROR(AO6-AN6,""),"")</f>
-        <v>-5.7851825593772332E-2</v>
+        <v>-5.7728672884412191E-2</v>
       </c>
     </row>
     <row r="7" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9768,12 +9769,14 @@
       <c r="AF7" s="57">
         <v>34.4</v>
       </c>
-      <c r="AG7" s="57"/>
+      <c r="AG7" s="57">
+        <v>35</v>
+      </c>
       <c r="AH7" s="57"/>
       <c r="AI7" s="57"/>
       <c r="AJ7" s="37">
         <f t="shared" si="0"/>
-        <v>34.4</v>
+        <v>35</v>
       </c>
       <c r="AK7" s="21">
         <f t="shared" si="1"/>
@@ -9791,11 +9794,11 @@
       </c>
       <c r="AO7" s="23">
         <f t="shared" si="3"/>
-        <v>35.360714285714288</v>
+        <v>35.348275862068959</v>
       </c>
       <c r="AP7" s="23">
         <f t="shared" si="4"/>
-        <v>1.9946982781452149</v>
+        <v>1.9822598544998868</v>
       </c>
     </row>
     <row r="8" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9895,12 +9898,14 @@
       <c r="AF8" s="57">
         <v>33.4</v>
       </c>
-      <c r="AG8" s="57"/>
+      <c r="AG8" s="57">
+        <v>34.299999999999997</v>
+      </c>
       <c r="AH8" s="57"/>
       <c r="AI8" s="57"/>
       <c r="AJ8" s="37">
         <f t="shared" si="0"/>
-        <v>33.4</v>
+        <v>34.299999999999997</v>
       </c>
       <c r="AK8" s="21">
         <f t="shared" si="1"/>
@@ -9918,11 +9923,11 @@
       </c>
       <c r="AO8" s="23">
         <f t="shared" si="3"/>
-        <v>33.153571428571432</v>
+        <v>33.193103448275863</v>
       </c>
       <c r="AP8" s="23">
         <f t="shared" si="4"/>
-        <v>0.90452841781873872</v>
+        <v>0.94406043752317004</v>
       </c>
     </row>
     <row r="9" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10022,12 +10027,14 @@
       <c r="AF9" s="57">
         <v>37.299999999999997</v>
       </c>
-      <c r="AG9" s="57"/>
+      <c r="AG9" s="57">
+        <v>34.9</v>
+      </c>
       <c r="AH9" s="57"/>
       <c r="AI9" s="57"/>
       <c r="AJ9" s="37">
         <f t="shared" si="0"/>
-        <v>37.299999999999997</v>
+        <v>34.9</v>
       </c>
       <c r="AK9" s="21">
         <f t="shared" si="1"/>
@@ -10045,11 +10052,11 @@
       </c>
       <c r="AO9" s="23">
         <f t="shared" si="3"/>
-        <v>33.910714285714285</v>
+        <v>33.944827586206891</v>
       </c>
       <c r="AP9" s="23">
         <f t="shared" si="4"/>
-        <v>0.81946814803043821</v>
+        <v>0.85358144852304463</v>
       </c>
     </row>
     <row r="10" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10149,12 +10156,14 @@
       <c r="AF10" s="57">
         <v>37.299999999999997</v>
       </c>
-      <c r="AG10" s="57"/>
+      <c r="AG10" s="57">
+        <v>37.200000000000003</v>
+      </c>
       <c r="AH10" s="57"/>
       <c r="AI10" s="57"/>
       <c r="AJ10" s="37">
         <f t="shared" si="0"/>
-        <v>37.299999999999997</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="AK10" s="21">
         <f t="shared" si="1"/>
@@ -10172,11 +10181,11 @@
       </c>
       <c r="AO10" s="23">
         <f t="shared" si="3"/>
-        <v>35.885714285714279</v>
+        <v>35.931034482758612</v>
       </c>
       <c r="AP10" s="23">
         <f t="shared" si="4"/>
-        <v>0.50547605805392237</v>
+        <v>0.55079625509825547</v>
       </c>
     </row>
     <row r="11" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10273,15 +10282,17 @@
       <c r="AE11" s="57">
         <v>37.6</v>
       </c>
-      <c r="AF11" s="81">
+      <c r="AF11" s="57">
         <v>40.799999999999997</v>
       </c>
-      <c r="AG11" s="57"/>
+      <c r="AG11" s="57">
+        <v>39.799999999999997</v>
+      </c>
       <c r="AH11" s="57"/>
       <c r="AI11" s="57"/>
       <c r="AJ11" s="37">
         <f t="shared" si="0"/>
-        <v>40.799999999999997</v>
+        <v>39.799999999999997</v>
       </c>
       <c r="AK11" s="21">
         <f t="shared" si="1"/>
@@ -10299,11 +10310,11 @@
       </c>
       <c r="AO11" s="23">
         <f t="shared" si="3"/>
-        <v>38.135714285714279</v>
+        <v>38.193103448275849</v>
       </c>
       <c r="AP11" s="23">
         <f t="shared" si="4"/>
-        <v>2.5984301928656777</v>
+        <v>2.6558193554272478</v>
       </c>
     </row>
     <row r="12" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10403,12 +10414,14 @@
       <c r="AF12" s="57">
         <v>34.6</v>
       </c>
-      <c r="AG12" s="57"/>
+      <c r="AG12" s="57">
+        <v>35.200000000000003</v>
+      </c>
       <c r="AH12" s="57"/>
       <c r="AI12" s="57"/>
       <c r="AJ12" s="37">
         <f t="shared" si="0"/>
-        <v>34.6</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="AK12" s="21">
         <f t="shared" si="1"/>
@@ -10426,11 +10439,11 @@
       </c>
       <c r="AO12" s="23">
         <f t="shared" si="3"/>
-        <v>34.628571428571426</v>
+        <v>34.648275862068964</v>
       </c>
       <c r="AP12" s="23">
         <f t="shared" si="4"/>
-        <v>2.4399472823976893</v>
+        <v>2.4596517158952267</v>
       </c>
     </row>
     <row r="13" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10530,12 +10543,14 @@
       <c r="AF13" s="57">
         <v>34.799999999999997</v>
       </c>
-      <c r="AG13" s="57"/>
+      <c r="AG13" s="57">
+        <v>35.6</v>
+      </c>
       <c r="AH13" s="57"/>
       <c r="AI13" s="57"/>
       <c r="AJ13" s="37">
         <f t="shared" si="0"/>
-        <v>34.799999999999997</v>
+        <v>35.6</v>
       </c>
       <c r="AK13" s="21">
         <f t="shared" si="1"/>
@@ -10553,11 +10568,11 @@
       </c>
       <c r="AO13" s="23">
         <f t="shared" si="3"/>
-        <v>35.299999999999997</v>
+        <v>35.310344827586206</v>
       </c>
       <c r="AP13" s="23">
         <f t="shared" si="4"/>
-        <v>1.9182078853046605</v>
+        <v>1.9285527128908697</v>
       </c>
     </row>
     <row r="14" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10657,12 +10672,14 @@
       <c r="AF14" s="57">
         <v>35.4</v>
       </c>
-      <c r="AG14" s="57"/>
+      <c r="AG14" s="57">
+        <v>36.299999999999997</v>
+      </c>
       <c r="AH14" s="57"/>
       <c r="AI14" s="57"/>
       <c r="AJ14" s="37">
         <f t="shared" si="0"/>
-        <v>35.4</v>
+        <v>36.299999999999997</v>
       </c>
       <c r="AK14" s="21">
         <f t="shared" si="1"/>
@@ -10680,11 +10697,11 @@
       </c>
       <c r="AO14" s="23">
         <f t="shared" si="3"/>
-        <v>34.624999999999993</v>
+        <v>34.682758620689647</v>
       </c>
       <c r="AP14" s="23">
         <f t="shared" si="4"/>
-        <v>1.4000634007857613</v>
+        <v>1.4578220214754154</v>
       </c>
     </row>
     <row r="15" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10784,12 +10801,14 @@
       <c r="AF15" s="57">
         <v>33.299999999999997</v>
       </c>
-      <c r="AG15" s="57"/>
+      <c r="AG15" s="57">
+        <v>33.200000000000003</v>
+      </c>
       <c r="AH15" s="57"/>
       <c r="AI15" s="57"/>
       <c r="AJ15" s="37">
         <f t="shared" si="0"/>
-        <v>33.299999999999997</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="AK15" s="21">
         <f t="shared" si="1"/>
@@ -10807,11 +10826,11 @@
       </c>
       <c r="AO15" s="23">
         <f t="shared" si="3"/>
-        <v>31.799999999999994</v>
+        <v>31.848275862068963</v>
       </c>
       <c r="AP15" s="23">
         <f t="shared" si="4"/>
-        <v>6.4662543920043447E-2</v>
+        <v>0.11293840598901284</v>
       </c>
     </row>
     <row r="16" spans="1:46" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10960,12 +10979,14 @@
       <c r="AF17" s="57">
         <v>35.299999999999997</v>
       </c>
-      <c r="AG17" s="57"/>
+      <c r="AG17" s="57">
+        <v>35.5</v>
+      </c>
       <c r="AH17" s="57"/>
       <c r="AI17" s="57"/>
       <c r="AJ17" s="37">
         <f t="shared" si="0"/>
-        <v>35.299999999999997</v>
+        <v>35.5</v>
       </c>
       <c r="AK17" s="21">
         <f t="shared" si="1"/>
@@ -10983,11 +11004,11 @@
       </c>
       <c r="AO17" s="23">
         <f>IF(COUNTIF(E17:AI17,"&gt;0")&gt;=15,AVERAGE(E17:AI17),"")</f>
-        <v>34.121428571428567</v>
+        <v>34.168965517241375</v>
       </c>
       <c r="AP17" s="23">
         <f>IF(AN17&gt;0,IFERROR(AO17-AN17,""),"")</f>
-        <v>1.4474463689814101</v>
+        <v>1.4949833147942186</v>
       </c>
     </row>
     <row r="18" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11087,12 +11108,14 @@
       <c r="AF18" s="57">
         <v>28.5</v>
       </c>
-      <c r="AG18" s="57"/>
+      <c r="AG18" s="57">
+        <v>28.7</v>
+      </c>
       <c r="AH18" s="57"/>
       <c r="AI18" s="57"/>
       <c r="AJ18" s="37">
         <f t="shared" si="0"/>
-        <v>28.5</v>
+        <v>28.7</v>
       </c>
       <c r="AK18" s="21">
         <f t="shared" si="1"/>
@@ -11110,11 +11133,11 @@
       </c>
       <c r="AO18" s="23">
         <f t="shared" ref="AO18:AO33" si="5">IF(COUNTIF(E18:AI18,"&gt;0")&gt;=15,AVERAGE(E18:AI18),"")</f>
-        <v>27.875000000000007</v>
+        <v>27.903448275862079</v>
       </c>
       <c r="AP18" s="23">
         <f t="shared" si="4"/>
-        <v>1.8151291460431374</v>
+        <v>1.8435774219052092</v>
       </c>
     </row>
     <row r="19" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11211,15 +11234,17 @@
       <c r="AE19" s="57">
         <v>35.4</v>
       </c>
-      <c r="AF19" s="80">
+      <c r="AF19" s="68">
         <v>37.6</v>
       </c>
-      <c r="AG19" s="57"/>
+      <c r="AG19" s="57">
+        <v>36.799999999999997</v>
+      </c>
       <c r="AH19" s="57"/>
       <c r="AI19" s="57"/>
       <c r="AJ19" s="37">
         <f t="shared" si="0"/>
-        <v>37.6</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="AK19" s="21">
         <f t="shared" si="1"/>
@@ -11237,11 +11262,11 @@
       </c>
       <c r="AO19" s="23">
         <f t="shared" si="5"/>
-        <v>33.971428571428568</v>
+        <v>34.068965517241374</v>
       </c>
       <c r="AP19" s="23">
         <f t="shared" si="4"/>
-        <v>0.72046616875892511</v>
+        <v>0.8180031145717308</v>
       </c>
     </row>
     <row r="20" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11341,12 +11366,14 @@
       <c r="AF20" s="57">
         <v>30.7</v>
       </c>
-      <c r="AG20" s="57"/>
+      <c r="AG20" s="57">
+        <v>31.1</v>
+      </c>
       <c r="AH20" s="57"/>
       <c r="AI20" s="57"/>
       <c r="AJ20" s="37">
         <f t="shared" si="0"/>
-        <v>30.7</v>
+        <v>31.1</v>
       </c>
       <c r="AK20" s="21">
         <f t="shared" si="1"/>
@@ -11364,11 +11391,11 @@
       </c>
       <c r="AO20" s="23">
         <f t="shared" si="5"/>
-        <v>30.178571428571434</v>
+        <v>30.210344827586212</v>
       </c>
       <c r="AP20" s="23">
         <f t="shared" si="4"/>
-        <v>1.5377668308702859</v>
+        <v>1.5695402298850638</v>
       </c>
     </row>
     <row r="21" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11468,12 +11495,14 @@
       <c r="AF21" s="57">
         <v>23.8</v>
       </c>
-      <c r="AG21" s="57"/>
+      <c r="AG21" s="57">
+        <v>24.2</v>
+      </c>
       <c r="AH21" s="57"/>
       <c r="AI21" s="57"/>
       <c r="AJ21" s="37">
         <f t="shared" si="0"/>
-        <v>23.8</v>
+        <v>24.2</v>
       </c>
       <c r="AK21" s="21">
         <f t="shared" si="1"/>
@@ -11491,11 +11520,11 @@
       </c>
       <c r="AO21" s="23">
         <f t="shared" si="5"/>
-        <v>24.203571428571422</v>
+        <v>24.203448275862065</v>
       </c>
       <c r="AP21" s="23">
         <f t="shared" si="4"/>
-        <v>1.5940682769214511</v>
+        <v>1.5939451242120946</v>
       </c>
     </row>
     <row r="22" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11663,12 +11692,14 @@
       <c r="AF23" s="57">
         <v>30.2</v>
       </c>
-      <c r="AG23" s="57"/>
+      <c r="AG23" s="57">
+        <v>30.5</v>
+      </c>
       <c r="AH23" s="57"/>
       <c r="AI23" s="57"/>
       <c r="AJ23" s="37">
         <f t="shared" si="0"/>
-        <v>30.2</v>
+        <v>30.5</v>
       </c>
       <c r="AK23" s="21">
         <f t="shared" si="1"/>
@@ -11686,11 +11717,11 @@
       </c>
       <c r="AO23" s="23">
         <f t="shared" si="5"/>
-        <v>28.585714285714289</v>
+        <v>28.651724137931037</v>
       </c>
       <c r="AP23" s="23">
         <f t="shared" si="4"/>
-        <v>1.7173271889400894</v>
+        <v>1.7833370411568374</v>
       </c>
     </row>
     <row r="24" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11790,12 +11821,14 @@
       <c r="AF24" s="57">
         <v>31.3</v>
       </c>
-      <c r="AG24" s="57"/>
+      <c r="AG24" s="57">
+        <v>31</v>
+      </c>
       <c r="AH24" s="57"/>
       <c r="AI24" s="57"/>
       <c r="AJ24" s="37">
         <f t="shared" si="0"/>
-        <v>31.3</v>
+        <v>31</v>
       </c>
       <c r="AK24" s="21">
         <f t="shared" si="1"/>
@@ -11813,11 +11846,11 @@
       </c>
       <c r="AO24" s="23">
         <f t="shared" si="5"/>
-        <v>29.50357142857143</v>
+        <v>29.555172413793105</v>
       </c>
       <c r="AP24" s="23">
         <f t="shared" si="4"/>
-        <v>1.2517473118279483</v>
+        <v>1.3033482970496237</v>
       </c>
     </row>
     <row r="25" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11917,12 +11950,14 @@
       <c r="AF25" s="57">
         <v>34</v>
       </c>
-      <c r="AG25" s="57"/>
+      <c r="AG25" s="57">
+        <v>32.1</v>
+      </c>
       <c r="AH25" s="57"/>
       <c r="AI25" s="57"/>
       <c r="AJ25" s="37">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>32.1</v>
       </c>
       <c r="AK25" s="21">
         <f t="shared" si="1"/>
@@ -11940,11 +11975,11 @@
       </c>
       <c r="AO25" s="23">
         <f t="shared" si="5"/>
-        <v>32.50714285714286</v>
+        <v>32.493103448275868</v>
       </c>
       <c r="AP25" s="23">
         <f t="shared" si="4"/>
-        <v>2.1312774639217906</v>
+        <v>2.1172380550547985</v>
       </c>
     </row>
     <row r="26" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12044,12 +12079,14 @@
       <c r="AF26" s="57">
         <v>21.08</v>
       </c>
-      <c r="AG26" s="57"/>
+      <c r="AG26" s="57">
+        <v>19.8</v>
+      </c>
       <c r="AH26" s="57"/>
       <c r="AI26" s="57"/>
       <c r="AJ26" s="37">
         <f t="shared" si="0"/>
-        <v>21.08</v>
+        <v>19.8</v>
       </c>
       <c r="AK26" s="21">
         <f t="shared" si="1"/>
@@ -12067,11 +12104,11 @@
       </c>
       <c r="AO26" s="23">
         <f t="shared" si="5"/>
-        <v>19.731428571428577</v>
+        <v>19.733793103448278</v>
       </c>
       <c r="AP26" s="23">
         <f t="shared" si="4"/>
-        <v>1.1885569639852172</v>
+        <v>1.1909214960049184</v>
       </c>
     </row>
     <row r="27" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12169,34 +12206,36 @@
       <c r="AF27" s="57">
         <v>21.2</v>
       </c>
-      <c r="AG27" s="57"/>
+      <c r="AG27" s="57">
+        <v>22.2</v>
+      </c>
       <c r="AH27" s="57"/>
       <c r="AI27" s="57"/>
       <c r="AJ27" s="37">
         <f t="shared" si="0"/>
-        <v>21.2</v>
+        <v>22.2</v>
       </c>
       <c r="AK27" s="21">
         <f t="shared" si="1"/>
-        <v>21.8</v>
+        <v>22.2</v>
       </c>
       <c r="AL27" s="22">
         <v>21.4</v>
       </c>
       <c r="AM27" s="23">
         <f t="shared" si="2"/>
-        <v>0.40000000000000213</v>
+        <v>0.80000000000000071</v>
       </c>
       <c r="AN27" s="23">
         <v>16.682050544108389</v>
       </c>
       <c r="AO27" s="23">
         <f t="shared" si="5"/>
-        <v>19.029629629629628</v>
+        <v>19.142857142857142</v>
       </c>
       <c r="AP27" s="23">
         <f t="shared" si="4"/>
-        <v>2.3475790855212395</v>
+        <v>2.4608065987487535</v>
       </c>
     </row>
     <row r="28" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12296,12 +12335,14 @@
       <c r="AF28" s="57">
         <v>32.6</v>
       </c>
-      <c r="AG28" s="57"/>
+      <c r="AG28" s="57">
+        <v>33.200000000000003</v>
+      </c>
       <c r="AH28" s="57"/>
       <c r="AI28" s="57"/>
       <c r="AJ28" s="37">
         <f t="shared" si="0"/>
-        <v>32.6</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="AK28" s="21">
         <f t="shared" si="1"/>
@@ -12319,11 +12360,11 @@
       </c>
       <c r="AO28" s="23">
         <f t="shared" si="5"/>
-        <v>31.928571428571434</v>
+        <v>31.972413793103453</v>
       </c>
       <c r="AP28" s="23">
         <f t="shared" si="4"/>
-        <v>1.4001188269152749</v>
+        <v>1.4439611914472934</v>
       </c>
     </row>
     <row r="29" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12489,12 +12530,14 @@
       <c r="AF30" s="57">
         <v>36.799999999999997</v>
       </c>
-      <c r="AG30" s="57"/>
+      <c r="AG30" s="57">
+        <v>36.200000000000003</v>
+      </c>
       <c r="AH30" s="57"/>
       <c r="AI30" s="57"/>
       <c r="AJ30" s="37">
         <f t="shared" si="0"/>
-        <v>36.799999999999997</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="AK30" s="21">
         <f t="shared" si="1"/>
@@ -12512,11 +12555,11 @@
       </c>
       <c r="AO30" s="23">
         <f t="shared" si="5"/>
-        <v>34.967857142857142</v>
+        <v>35.010344827586209</v>
       </c>
       <c r="AP30" s="23">
         <f t="shared" si="4"/>
-        <v>1.2256062467997921</v>
+        <v>1.2680939315288597</v>
       </c>
     </row>
     <row r="31" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12616,12 +12659,14 @@
       <c r="AF31" s="57">
         <v>28.3</v>
       </c>
-      <c r="AG31" s="57"/>
+      <c r="AG31" s="57">
+        <v>28.2</v>
+      </c>
       <c r="AH31" s="57"/>
       <c r="AI31" s="57"/>
       <c r="AJ31" s="37">
         <f t="shared" si="0"/>
-        <v>28.3</v>
+        <v>28.2</v>
       </c>
       <c r="AK31" s="21">
         <f t="shared" si="1"/>
@@ -12639,11 +12684,11 @@
       </c>
       <c r="AO31" s="23">
         <f t="shared" si="5"/>
-        <v>27.278571428571428</v>
+        <v>27.310344827586206</v>
       </c>
       <c r="AP31" s="23">
         <f t="shared" si="4"/>
-        <v>1.8911465914508092</v>
+        <v>1.9229199904655871</v>
       </c>
     </row>
     <row r="32" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12743,12 +12788,14 @@
       <c r="AF32" s="57">
         <v>18.399999999999999</v>
       </c>
-      <c r="AG32" s="57"/>
+      <c r="AG32" s="57">
+        <v>18</v>
+      </c>
       <c r="AH32" s="57"/>
       <c r="AI32" s="57"/>
       <c r="AJ32" s="37">
         <f t="shared" si="0"/>
-        <v>18.399999999999999</v>
+        <v>18</v>
       </c>
       <c r="AK32" s="21">
         <f t="shared" si="1"/>
@@ -12766,11 +12813,11 @@
       </c>
       <c r="AO32" s="23">
         <f t="shared" si="5"/>
-        <v>17.792857142857144</v>
+        <v>17.8</v>
       </c>
       <c r="AP32" s="23">
         <f t="shared" si="4"/>
-        <v>1.4633193695958937</v>
+        <v>1.4704622267387499</v>
       </c>
     </row>
     <row r="33" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12870,12 +12917,14 @@
       <c r="AF33" s="57">
         <v>15</v>
       </c>
-      <c r="AG33" s="57"/>
+      <c r="AG33" s="57">
+        <v>15.3</v>
+      </c>
       <c r="AH33" s="57"/>
       <c r="AI33" s="57"/>
       <c r="AJ33" s="37">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>15.3</v>
       </c>
       <c r="AK33" s="21">
         <f t="shared" si="1"/>
@@ -12893,11 +12942,11 @@
       </c>
       <c r="AO33" s="23">
         <f t="shared" si="5"/>
-        <v>15.625</v>
+        <v>15.613793103448277</v>
       </c>
       <c r="AP33" s="23">
         <f t="shared" si="4"/>
-        <v>0.88038746755655062</v>
+        <v>0.86918057100482748</v>
       </c>
       <c r="AT33" s="15"/>
     </row>
@@ -13049,12 +13098,14 @@
       <c r="AF35" s="57">
         <v>33.6</v>
       </c>
-      <c r="AG35" s="57"/>
+      <c r="AG35" s="57">
+        <v>34.200000000000003</v>
+      </c>
       <c r="AH35" s="57"/>
       <c r="AI35" s="57"/>
       <c r="AJ35" s="37">
         <f t="shared" si="0"/>
-        <v>33.6</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="AK35" s="21">
         <f t="shared" si="1"/>
@@ -13072,11 +13123,11 @@
       </c>
       <c r="AO35" s="23">
         <f>IF(COUNTIF(E35:AI35,"&gt;0")&gt;=15,AVERAGE(E35:AI35),"")</f>
-        <v>31.914285714285711</v>
+        <v>31.993103448275861</v>
       </c>
       <c r="AP35" s="23">
         <f t="shared" si="4"/>
-        <v>0.84158986175114947</v>
+        <v>0.92040759574129893</v>
       </c>
       <c r="AT35" s="15"/>
     </row>
@@ -13297,12 +13348,14 @@
       <c r="AF38" s="57">
         <v>33.4</v>
       </c>
-      <c r="AG38" s="57"/>
+      <c r="AG38" s="57">
+        <v>30.7</v>
+      </c>
       <c r="AH38" s="57"/>
       <c r="AI38" s="57"/>
       <c r="AJ38" s="37">
         <f t="shared" si="0"/>
-        <v>33.4</v>
+        <v>30.7</v>
       </c>
       <c r="AK38" s="21">
         <f t="shared" si="1"/>
@@ -13320,11 +13373,11 @@
       </c>
       <c r="AO38" s="23">
         <f>IF(COUNTIF(E38:AI38,"&gt;0")&gt;=15,AVERAGE(E38:AI38),"")</f>
-        <v>30.182142857142853</v>
+        <v>30.2</v>
       </c>
       <c r="AP38" s="23">
         <f t="shared" si="4"/>
-        <v>0.15311663375027251</v>
+        <v>0.17097377660741842</v>
       </c>
       <c r="AT38" s="15"/>
     </row>
@@ -13425,12 +13478,14 @@
       <c r="AF39" s="57">
         <v>32.4</v>
       </c>
-      <c r="AG39" s="57"/>
+      <c r="AG39" s="57">
+        <v>33.6</v>
+      </c>
       <c r="AH39" s="57"/>
       <c r="AI39" s="57"/>
       <c r="AJ39" s="37">
         <f t="shared" si="0"/>
-        <v>32.4</v>
+        <v>33.6</v>
       </c>
       <c r="AK39" s="21">
         <f t="shared" si="1"/>
@@ -13448,11 +13503,11 @@
       </c>
       <c r="AO39" s="23">
         <f t="shared" ref="AO39:AO48" si="7">IF(COUNTIF(E39:AI39,"&gt;0")&gt;=15,AVERAGE(E39:AI39),"")</f>
-        <v>31.532142857142855</v>
+        <v>31.603448275862068</v>
       </c>
       <c r="AP39" s="23">
         <f t="shared" si="4"/>
-        <v>0.68900974627893419</v>
+        <v>0.760315164998147</v>
       </c>
       <c r="AT39" s="15"/>
     </row>
@@ -13553,12 +13608,14 @@
       <c r="AF40" s="57">
         <v>32.200000000000003</v>
       </c>
-      <c r="AG40" s="57"/>
+      <c r="AG40" s="57">
+        <v>28.8</v>
+      </c>
       <c r="AH40" s="57"/>
       <c r="AI40" s="57"/>
       <c r="AJ40" s="37">
         <f t="shared" si="0"/>
-        <v>32.200000000000003</v>
+        <v>28.8</v>
       </c>
       <c r="AK40" s="21">
         <f t="shared" si="1"/>
@@ -13576,11 +13633,11 @@
       </c>
       <c r="AO40" s="23">
         <f t="shared" si="7"/>
-        <v>30.046428571428574</v>
+        <v>30.00344827586207</v>
       </c>
       <c r="AP40" s="23">
         <f t="shared" si="4"/>
-        <v>1.0988801843317937</v>
+        <v>1.0558998887652891</v>
       </c>
       <c r="AT40" s="15"/>
     </row>
@@ -13681,12 +13738,14 @@
       <c r="AF41" s="57">
         <v>33</v>
       </c>
-      <c r="AG41" s="57"/>
+      <c r="AG41" s="57">
+        <v>33.200000000000003</v>
+      </c>
       <c r="AH41" s="57"/>
       <c r="AI41" s="57"/>
       <c r="AJ41" s="37">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="AK41" s="21">
         <f t="shared" si="1"/>
@@ -13704,11 +13763,11 @@
       </c>
       <c r="AO41" s="23">
         <f t="shared" si="7"/>
-        <v>30.714285714285722</v>
+        <v>30.800000000000008</v>
       </c>
       <c r="AP41" s="23">
         <f t="shared" si="4"/>
-        <v>1.3479774705581313</v>
+        <v>1.4336917562724167</v>
       </c>
       <c r="AT41" s="15"/>
     </row>
@@ -13870,12 +13929,14 @@
       <c r="AF43" s="57">
         <v>32.799999999999997</v>
       </c>
-      <c r="AG43" s="57"/>
+      <c r="AG43" s="57">
+        <v>33.4</v>
+      </c>
       <c r="AH43" s="57"/>
       <c r="AI43" s="57"/>
       <c r="AJ43" s="37">
         <f t="shared" si="0"/>
-        <v>32.799999999999997</v>
+        <v>33.4</v>
       </c>
       <c r="AK43" s="21">
         <f t="shared" si="1"/>
@@ -13893,11 +13954,11 @@
       </c>
       <c r="AO43" s="23">
         <f t="shared" si="7"/>
-        <v>31.335999999999999</v>
+        <v>31.415384615384614</v>
       </c>
       <c r="AP43" s="23">
         <f t="shared" si="4"/>
-        <v>1.274938172043008</v>
+        <v>1.3543227874276234</v>
       </c>
       <c r="AT43" s="15"/>
     </row>
@@ -13996,12 +14057,14 @@
       <c r="AF44" s="57">
         <v>31.2</v>
       </c>
-      <c r="AG44" s="57"/>
+      <c r="AG44" s="57">
+        <v>32</v>
+      </c>
       <c r="AH44" s="57"/>
       <c r="AI44" s="57"/>
       <c r="AJ44" s="37">
         <f t="shared" si="0"/>
-        <v>31.2</v>
+        <v>32</v>
       </c>
       <c r="AK44" s="21">
         <f t="shared" si="1"/>
@@ -14019,11 +14082,11 @@
       </c>
       <c r="AO44" s="23">
         <f t="shared" si="7"/>
-        <v>31.288888888888888</v>
+        <v>31.314285714285713</v>
       </c>
       <c r="AP44" s="23">
         <f t="shared" si="4"/>
-        <v>2.2457016835284271</v>
+        <v>2.2710985089252524</v>
       </c>
       <c r="AT44" s="15"/>
     </row>
@@ -14124,12 +14187,14 @@
       <c r="AF45" s="57">
         <v>32</v>
       </c>
-      <c r="AG45" s="57"/>
+      <c r="AG45" s="57">
+        <v>33</v>
+      </c>
       <c r="AH45" s="57"/>
       <c r="AI45" s="57"/>
       <c r="AJ45" s="37">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AK45" s="21">
         <f t="shared" si="1"/>
@@ -14147,11 +14212,11 @@
       </c>
       <c r="AO45" s="23">
         <f t="shared" si="7"/>
-        <v>30.735714285714295</v>
+        <v>30.813793103448283</v>
       </c>
       <c r="AP45" s="23">
         <f t="shared" si="4"/>
-        <v>1.1898978928354644</v>
+        <v>1.267976710569453</v>
       </c>
       <c r="AT45" s="15"/>
     </row>
@@ -14391,12 +14456,14 @@
       <c r="AF48" s="57">
         <v>32.1</v>
       </c>
-      <c r="AG48" s="57"/>
+      <c r="AG48" s="57">
+        <v>32.4</v>
+      </c>
       <c r="AH48" s="57"/>
       <c r="AI48" s="57"/>
       <c r="AJ48" s="37">
         <f t="shared" si="0"/>
-        <v>32.1</v>
+        <v>32.4</v>
       </c>
       <c r="AK48" s="21">
         <f t="shared" si="1"/>
@@ -14414,11 +14481,11 @@
       </c>
       <c r="AO48" s="23">
         <f t="shared" si="7"/>
-        <v>30.757142857142863</v>
+        <v>30.81379310344828</v>
       </c>
       <c r="AP48" s="23">
         <f t="shared" si="4"/>
-        <v>0.41461000170678375</v>
+        <v>0.47126024801220012</v>
       </c>
     </row>
     <row r="49" spans="5:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -20760,66 +20827,66 @@
       <c r="E1" s="52"/>
       <c r="F1" s="52"/>
       <c r="G1" s="52"/>
-      <c r="H1" s="72" t="s">
+      <c r="H1" s="73" t="s">
         <v>123</v>
       </c>
-      <c r="I1" s="73"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="69" t="s">
+      <c r="I1" s="74"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="70" t="s">
         <v>124</v>
       </c>
-      <c r="L1" s="70"/>
-      <c r="M1" s="71"/>
-      <c r="N1" s="72" t="s">
+      <c r="L1" s="71"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="73" t="s">
         <v>125</v>
       </c>
-      <c r="O1" s="73"/>
-      <c r="P1" s="74"/>
-      <c r="Q1" s="69" t="s">
+      <c r="O1" s="74"/>
+      <c r="P1" s="75"/>
+      <c r="Q1" s="70" t="s">
         <v>126</v>
       </c>
-      <c r="R1" s="70"/>
-      <c r="S1" s="71"/>
-      <c r="T1" s="72" t="s">
+      <c r="R1" s="71"/>
+      <c r="S1" s="72"/>
+      <c r="T1" s="73" t="s">
         <v>127</v>
       </c>
-      <c r="U1" s="73"/>
-      <c r="V1" s="74"/>
-      <c r="W1" s="69" t="s">
+      <c r="U1" s="74"/>
+      <c r="V1" s="75"/>
+      <c r="W1" s="70" t="s">
         <v>128</v>
       </c>
-      <c r="X1" s="70"/>
-      <c r="Y1" s="71"/>
-      <c r="Z1" s="72" t="s">
+      <c r="X1" s="71"/>
+      <c r="Y1" s="72"/>
+      <c r="Z1" s="73" t="s">
         <v>129</v>
       </c>
-      <c r="AA1" s="73"/>
-      <c r="AB1" s="74"/>
-      <c r="AC1" s="69" t="s">
+      <c r="AA1" s="74"/>
+      <c r="AB1" s="75"/>
+      <c r="AC1" s="70" t="s">
         <v>130</v>
       </c>
-      <c r="AD1" s="70"/>
-      <c r="AE1" s="71"/>
-      <c r="AF1" s="72" t="s">
+      <c r="AD1" s="71"/>
+      <c r="AE1" s="72"/>
+      <c r="AF1" s="73" t="s">
         <v>131</v>
       </c>
-      <c r="AG1" s="73"/>
-      <c r="AH1" s="74"/>
-      <c r="AI1" s="69" t="s">
+      <c r="AG1" s="74"/>
+      <c r="AH1" s="75"/>
+      <c r="AI1" s="70" t="s">
         <v>132</v>
       </c>
-      <c r="AJ1" s="70"/>
-      <c r="AK1" s="71"/>
-      <c r="AL1" s="72" t="s">
+      <c r="AJ1" s="71"/>
+      <c r="AK1" s="72"/>
+      <c r="AL1" s="73" t="s">
         <v>133</v>
       </c>
-      <c r="AM1" s="73"/>
-      <c r="AN1" s="74"/>
-      <c r="AO1" s="69" t="s">
+      <c r="AM1" s="74"/>
+      <c r="AN1" s="75"/>
+      <c r="AO1" s="70" t="s">
         <v>134</v>
       </c>
-      <c r="AP1" s="70"/>
-      <c r="AQ1" s="71"/>
+      <c r="AP1" s="71"/>
+      <c r="AQ1" s="72"/>
     </row>
     <row r="2" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A2" s="54" t="s">
@@ -26256,68 +26323,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="79" t="s">
+      <c r="B1" s="80" t="s">
         <v>93</v>
       </c>
-      <c r="C1" s="68" t="s">
+      <c r="C1" s="69" t="s">
         <v>94</v>
       </c>
-      <c r="D1" s="75" t="s">
+      <c r="D1" s="76" t="s">
         <v>95</v>
       </c>
-      <c r="E1" s="75" t="s">
+      <c r="E1" s="76" t="s">
         <v>96</v>
       </c>
-      <c r="F1" s="75" t="s">
+      <c r="F1" s="76" t="s">
         <v>97</v>
       </c>
-      <c r="G1" s="75" t="s">
+      <c r="G1" s="76" t="s">
         <v>98</v>
       </c>
-      <c r="H1" s="75" t="s">
+      <c r="H1" s="76" t="s">
         <v>99</v>
       </c>
-      <c r="I1" s="75" t="s">
+      <c r="I1" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="J1" s="75" t="s">
+      <c r="J1" s="76" t="s">
         <v>101</v>
       </c>
-      <c r="K1" s="75" t="s">
+      <c r="K1" s="76" t="s">
         <v>102</v>
       </c>
-      <c r="L1" s="75" t="s">
+      <c r="L1" s="76" t="s">
         <v>103</v>
       </c>
-      <c r="M1" s="75" t="s">
+      <c r="M1" s="76" t="s">
         <v>104</v>
       </c>
-      <c r="N1" s="75" t="s">
+      <c r="N1" s="76" t="s">
         <v>105</v>
       </c>
-      <c r="O1" s="75" t="s">
+      <c r="O1" s="76" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="78"/>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="76"/>
-      <c r="M2" s="76"/>
-      <c r="N2" s="76"/>
-      <c r="O2" s="76"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="77"/>
+      <c r="O2" s="77"/>
     </row>
     <row r="3" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3"/>
@@ -27317,12 +27384,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
     <mergeCell ref="M1:M2"/>
     <mergeCell ref="N1:N2"/>
     <mergeCell ref="O1:O2"/>
@@ -27332,6 +27393,12 @@
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="L1:L2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:O13 D15:O31 D33:O34 D36:O46">
     <cfRule type="cellIs" dxfId="0" priority="1" stopIfTrue="1" operator="equal">
